--- a/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8277" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8277" uniqueCount="799">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T16:14:22+00:00</t>
+    <t>2025-03-08T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1176,9 +1176,6 @@
   </si>
   <si>
     <t>Appointment.participant:HL7ATCorePatient.actor.display</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
   </si>
   <si>
     <t>Appointment.participant:HL7ATCorePatient.required</t>
@@ -2832,7 +2829,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="23">
@@ -2840,7 +2837,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="24">
@@ -2856,7 +2853,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="26">
@@ -2864,7 +2861,7 @@
         <v>10</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="27">
@@ -2910,7 +2907,7 @@
         <v>21</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="33">
@@ -2946,7 +2943,7 @@
         <v>29</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38">
@@ -2954,7 +2951,7 @@
         <v>31</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="39">
@@ -2986,7 +2983,7 @@
         <v>2</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="43">
@@ -2994,7 +2991,7 @@
         <v>4</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="44">
@@ -3010,7 +3007,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="46">
@@ -3018,7 +3015,7 @@
         <v>10</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="47">
@@ -3064,7 +3061,7 @@
         <v>21</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="53">
@@ -3100,7 +3097,7 @@
         <v>29</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="58">
@@ -3108,7 +3105,7 @@
         <v>31</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="59">
@@ -3140,7 +3137,7 @@
         <v>2</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="63">
@@ -3148,7 +3145,7 @@
         <v>4</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="64">
@@ -3164,7 +3161,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="66">
@@ -3172,7 +3169,7 @@
         <v>10</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="67">
@@ -3218,7 +3215,7 @@
         <v>21</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="73">
@@ -3254,7 +3251,7 @@
         <v>29</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="78">
@@ -3262,7 +3259,7 @@
         <v>31</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="79">
@@ -3294,7 +3291,7 @@
         <v>2</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="83">
@@ -3302,7 +3299,7 @@
         <v>4</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="84">
@@ -3318,7 +3315,7 @@
         <v>8</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="86">
@@ -3326,7 +3323,7 @@
         <v>10</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="87">
@@ -3372,7 +3369,7 @@
         <v>21</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="93">
@@ -3408,7 +3405,7 @@
         <v>29</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="98">
@@ -3416,7 +3413,7 @@
         <v>31</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="99">
@@ -10285,7 +10282,7 @@
         <v>80</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>20</v>
@@ -10303,7 +10300,7 @@
         <v>334</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>361</v>
+        <v>175</v>
       </c>
       <c r="P66" s="2"/>
       <c r="Q66" t="s" s="2">
@@ -10373,7 +10370,7 @@
         <v>3</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>336</v>
@@ -10478,7 +10475,7 @@
         <v>3</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>341</v>
@@ -10495,7 +10492,7 @@
         <v>80</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>20</v>
@@ -10581,13 +10578,13 @@
         <v>3</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>274</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E69" t="s" s="2">
         <v>20</v>
@@ -10686,7 +10683,7 @@
         <v>3</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>281</v>
@@ -10789,7 +10786,7 @@
         <v>3</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>286</v>
@@ -10894,7 +10891,7 @@
         <v>3</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>289</v>
@@ -11001,7 +10998,7 @@
         <v>3</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>294</v>
@@ -11106,7 +11103,7 @@
         <v>3</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>301</v>
@@ -11209,7 +11206,7 @@
         <v>3</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>304</v>
@@ -11235,7 +11232,7 @@
         <v>81</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>306</v>
@@ -11314,7 +11311,7 @@
         <v>3</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>309</v>
@@ -11417,7 +11414,7 @@
         <v>3</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>310</v>
@@ -11522,7 +11519,7 @@
         <v>3</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>313</v>
@@ -11627,7 +11624,7 @@
         <v>3</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>319</v>
@@ -11732,7 +11729,7 @@
         <v>3</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C80" t="s" s="2">
         <v>326</v>
@@ -11837,7 +11834,7 @@
         <v>3</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>332</v>
@@ -11854,7 +11851,7 @@
         <v>80</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>20</v>
@@ -11872,7 +11869,7 @@
         <v>334</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>361</v>
+        <v>175</v>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" t="s" s="2">
@@ -11942,7 +11939,7 @@
         <v>3</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C82" t="s" s="2">
         <v>336</v>
@@ -12047,7 +12044,7 @@
         <v>3</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>341</v>
@@ -12064,7 +12061,7 @@
         <v>80</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>20</v>
@@ -12150,13 +12147,13 @@
         <v>3</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>274</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E84" t="s" s="2">
         <v>20</v>
@@ -12255,7 +12252,7 @@
         <v>3</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>281</v>
@@ -12358,7 +12355,7 @@
         <v>3</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>286</v>
@@ -12463,7 +12460,7 @@
         <v>3</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>289</v>
@@ -12570,7 +12567,7 @@
         <v>3</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C88" t="s" s="2">
         <v>294</v>
@@ -12675,7 +12672,7 @@
         <v>3</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>301</v>
@@ -12778,7 +12775,7 @@
         <v>3</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>304</v>
@@ -12804,7 +12801,7 @@
         <v>81</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>306</v>
@@ -12883,7 +12880,7 @@
         <v>3</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>309</v>
@@ -12986,7 +12983,7 @@
         <v>3</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>310</v>
@@ -13091,7 +13088,7 @@
         <v>3</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>313</v>
@@ -13196,7 +13193,7 @@
         <v>3</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>319</v>
@@ -13301,7 +13298,7 @@
         <v>3</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>326</v>
@@ -13406,7 +13403,7 @@
         <v>3</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>332</v>
@@ -13423,7 +13420,7 @@
         <v>80</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="J96" t="s" s="2">
         <v>20</v>
@@ -13441,7 +13438,7 @@
         <v>334</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>361</v>
+        <v>175</v>
       </c>
       <c r="P96" s="2"/>
       <c r="Q96" t="s" s="2">
@@ -13511,7 +13508,7 @@
         <v>3</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>336</v>
@@ -13616,7 +13613,7 @@
         <v>3</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>341</v>
@@ -13633,7 +13630,7 @@
         <v>80</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="J98" t="s" s="2">
         <v>20</v>
@@ -13719,13 +13716,13 @@
         <v>3</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>274</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E99" t="s" s="2">
         <v>20</v>
@@ -13824,7 +13821,7 @@
         <v>3</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>281</v>
@@ -13927,7 +13924,7 @@
         <v>3</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>286</v>
@@ -14032,7 +14029,7 @@
         <v>3</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>289</v>
@@ -14139,7 +14136,7 @@
         <v>3</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>294</v>
@@ -14244,7 +14241,7 @@
         <v>3</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>301</v>
@@ -14347,7 +14344,7 @@
         <v>3</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>304</v>
@@ -14373,7 +14370,7 @@
         <v>81</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>306</v>
@@ -14452,7 +14449,7 @@
         <v>3</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>309</v>
@@ -14555,7 +14552,7 @@
         <v>3</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>310</v>
@@ -14660,7 +14657,7 @@
         <v>3</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>313</v>
@@ -14765,7 +14762,7 @@
         <v>3</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C109" t="s" s="2">
         <v>319</v>
@@ -14870,7 +14867,7 @@
         <v>3</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C110" t="s" s="2">
         <v>326</v>
@@ -14975,7 +14972,7 @@
         <v>3</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C111" t="s" s="2">
         <v>332</v>
@@ -15080,7 +15077,7 @@
         <v>3</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>336</v>
@@ -15185,7 +15182,7 @@
         <v>3</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>341</v>
@@ -15288,10 +15285,10 @@
         <v>3</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -15317,10 +15314,10 @@
         <v>229</v>
       </c>
       <c r="M114" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N114" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" s="2"/>
@@ -15371,7 +15368,7 @@
         <v>20</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>73</v>
@@ -15391,10 +15388,10 @@
         <v>3</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -15420,13 +15417,13 @@
         <v>337</v>
       </c>
       <c r="M115" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N115" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="P115" s="2"/>
       <c r="Q115" t="s" s="2">
@@ -15476,7 +15473,7 @@
         <v>20</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>73</v>
@@ -15496,10 +15493,10 @@
         <v>3</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -15525,10 +15522,10 @@
         <v>275</v>
       </c>
       <c r="M116" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
@@ -15579,7 +15576,7 @@
         <v>20</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>73</v>
@@ -15599,10 +15596,10 @@
         <v>3</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -15702,10 +15699,10 @@
         <v>3</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -15807,10 +15804,10 @@
         <v>3</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -15914,10 +15911,10 @@
         <v>3</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -15943,10 +15940,10 @@
         <v>149</v>
       </c>
       <c r="M120" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N120" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
@@ -15976,11 +15973,11 @@
         <v>104</v>
       </c>
       <c r="Z120" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AA120" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AA120" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AB120" t="s" s="2">
         <v>20</v>
       </c>
@@ -15997,7 +15994,7 @@
         <v>20</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>73</v>
@@ -16017,10 +16014,10 @@
         <v>3</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -16046,10 +16043,10 @@
         <v>149</v>
       </c>
       <c r="M121" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N121" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
@@ -16079,10 +16076,10 @@
         <v>158</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AA121" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AB121" t="s" s="2">
         <v>20</v>
@@ -16100,7 +16097,7 @@
         <v>20</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>80</v>
@@ -16120,10 +16117,10 @@
         <v>3</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -16146,13 +16143,13 @@
         <v>20</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
@@ -16203,7 +16200,7 @@
         <v>20</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>73</v>
@@ -16223,10 +16220,10 @@
         <v>3</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -16252,10 +16249,10 @@
         <v>229</v>
       </c>
       <c r="M123" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N123" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
@@ -16306,7 +16303,7 @@
         <v>20</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>73</v>
@@ -16326,10 +16323,10 @@
         <v>3</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -16352,13 +16349,13 @@
         <v>20</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M124" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N124" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
@@ -16409,7 +16406,7 @@
         <v>20</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>73</v>
@@ -16429,10 +16426,10 @@
         <v>3</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -16458,10 +16455,10 @@
         <v>275</v>
       </c>
       <c r="M125" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N125" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
@@ -16512,7 +16509,7 @@
         <v>20</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>73</v>
@@ -16532,10 +16529,10 @@
         <v>3</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -16635,10 +16632,10 @@
         <v>3</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -16740,10 +16737,10 @@
         <v>3</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -16847,10 +16844,10 @@
         <v>3</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -16876,10 +16873,10 @@
         <v>337</v>
       </c>
       <c r="M129" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" s="2"/>
@@ -16930,7 +16927,7 @@
         <v>20</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>73</v>
@@ -16950,10 +16947,10 @@
         <v>3</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -16979,10 +16976,10 @@
         <v>337</v>
       </c>
       <c r="M130" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
@@ -17033,7 +17030,7 @@
         <v>20</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>73</v>
@@ -17053,10 +17050,10 @@
         <v>3</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -17082,10 +17079,10 @@
         <v>337</v>
       </c>
       <c r="M131" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
@@ -17136,7 +17133,7 @@
         <v>20</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>73</v>
@@ -17156,10 +17153,10 @@
         <v>3</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -17185,10 +17182,10 @@
         <v>337</v>
       </c>
       <c r="M132" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N132" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
@@ -17239,7 +17236,7 @@
         <v>20</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>73</v>
@@ -17259,10 +17256,10 @@
         <v>3</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -17288,10 +17285,10 @@
         <v>337</v>
       </c>
       <c r="M133" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
@@ -17342,7 +17339,7 @@
         <v>20</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>73</v>
@@ -17362,10 +17359,10 @@
         <v>3</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -17391,10 +17388,10 @@
         <v>337</v>
       </c>
       <c r="M134" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
@@ -17445,7 +17442,7 @@
         <v>20</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>73</v>
@@ -17465,10 +17462,10 @@
         <v>3</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -17494,10 +17491,10 @@
         <v>337</v>
       </c>
       <c r="M135" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N135" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
@@ -17548,7 +17545,7 @@
         <v>20</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>73</v>
@@ -17568,10 +17565,10 @@
         <v>3</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -17597,10 +17594,10 @@
         <v>229</v>
       </c>
       <c r="M136" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N136" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" s="2"/>
@@ -17651,7 +17648,7 @@
         <v>20</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>73</v>
@@ -17671,10 +17668,10 @@
         <v>3</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -17700,10 +17697,10 @@
         <v>275</v>
       </c>
       <c r="M137" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N137" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" s="2"/>
@@ -17754,7 +17751,7 @@
         <v>20</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>73</v>
@@ -17774,10 +17771,10 @@
         <v>3</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -17877,10 +17874,10 @@
         <v>3</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -17982,10 +17979,10 @@
         <v>3</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -18089,10 +18086,10 @@
         <v>3</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -18118,10 +18115,10 @@
         <v>229</v>
       </c>
       <c r="M141" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N141" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" s="2"/>
@@ -18172,7 +18169,7 @@
         <v>20</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>73</v>
@@ -18192,10 +18189,10 @@
         <v>3</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -18218,13 +18215,13 @@
         <v>20</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
@@ -18254,11 +18251,11 @@
         <v>104</v>
       </c>
       <c r="Z142" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AA142" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AA142" t="s" s="2">
-        <v>491</v>
-      </c>
       <c r="AB142" t="s" s="2">
         <v>20</v>
       </c>
@@ -18275,7 +18272,7 @@
         <v>20</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>73</v>
@@ -18295,10 +18292,10 @@
         <v>3</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -18321,16 +18318,16 @@
         <v>20</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M143" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="N143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P143" s="2"/>
       <c r="Q143" t="s" s="2">
@@ -18359,11 +18356,11 @@
         <v>104</v>
       </c>
       <c r="Z143" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AA143" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AA143" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="AB143" t="s" s="2">
         <v>20</v>
       </c>
@@ -18380,7 +18377,7 @@
         <v>20</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>73</v>
@@ -18400,10 +18397,10 @@
         <v>3</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -18429,10 +18426,10 @@
         <v>229</v>
       </c>
       <c r="M144" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N144" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
@@ -18483,7 +18480,7 @@
         <v>20</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>80</v>
@@ -18503,10 +18500,10 @@
         <v>3</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -18532,10 +18529,10 @@
         <v>275</v>
       </c>
       <c r="M145" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N145" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
@@ -18586,7 +18583,7 @@
         <v>20</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>73</v>
@@ -18606,10 +18603,10 @@
         <v>3</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -18709,10 +18706,10 @@
         <v>3</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -18814,10 +18811,10 @@
         <v>3</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -18921,10 +18918,10 @@
         <v>3</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -18950,10 +18947,10 @@
         <v>229</v>
       </c>
       <c r="M149" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
@@ -19004,7 +19001,7 @@
         <v>20</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>80</v>
@@ -19024,10 +19021,10 @@
         <v>3</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -19050,16 +19047,16 @@
         <v>20</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M150" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N150" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="N150" t="s" s="2">
+      <c r="O150" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="P150" s="2"/>
       <c r="Q150" t="s" s="2">
@@ -19109,7 +19106,7 @@
         <v>20</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>73</v>
@@ -19129,10 +19126,10 @@
         <v>3</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -19158,13 +19155,13 @@
         <v>229</v>
       </c>
       <c r="M151" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O151" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="P151" s="2"/>
       <c r="Q151" t="s" s="2">
@@ -19214,7 +19211,7 @@
         <v>20</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>73</v>
@@ -19231,13 +19228,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -19263,10 +19260,10 @@
         <v>75</v>
       </c>
       <c r="M152" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N152" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
@@ -19317,7 +19314,7 @@
         <v>20</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>73</v>
@@ -19329,18 +19326,18 @@
         <v>20</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -19439,13 +19436,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -19542,13 +19539,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -19647,13 +19644,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -19752,13 +19749,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -19857,13 +19854,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -19962,13 +19959,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -20067,13 +20064,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -20174,13 +20171,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -20209,7 +20206,7 @@
         <v>139</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
@@ -20260,7 +20257,7 @@
         <v>20</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>73</v>
@@ -20277,13 +20274,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -20309,10 +20306,10 @@
         <v>198</v>
       </c>
       <c r="M162" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N162" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
@@ -20363,7 +20360,7 @@
         <v>20</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>80</v>
@@ -20380,13 +20377,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -20412,10 +20409,10 @@
         <v>337</v>
       </c>
       <c r="M163" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N163" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
@@ -20466,7 +20463,7 @@
         <v>20</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>73</v>
@@ -20483,13 +20480,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -20515,13 +20512,13 @@
         <v>220</v>
       </c>
       <c r="M164" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N164" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="N164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="P164" s="2"/>
       <c r="Q164" t="s" s="2">
@@ -20571,7 +20568,7 @@
         <v>20</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>73</v>
@@ -20588,13 +20585,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -20620,10 +20617,10 @@
         <v>220</v>
       </c>
       <c r="M165" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="N165" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
@@ -20674,7 +20671,7 @@
         <v>20</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>73</v>
@@ -20691,13 +20688,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -20729,7 +20726,7 @@
         <v>296</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="P166" s="2"/>
       <c r="Q166" t="s" s="2">
@@ -20779,7 +20776,7 @@
         <v>20</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>73</v>
@@ -20788,7 +20785,7 @@
         <v>74</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>92</v>
@@ -20796,13 +20793,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -20825,13 +20822,13 @@
         <v>81</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
@@ -20882,7 +20879,7 @@
         <v>20</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>73</v>
@@ -20891,7 +20888,7 @@
         <v>80</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>92</v>
@@ -20899,13 +20896,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -20931,13 +20928,13 @@
         <v>100</v>
       </c>
       <c r="M168" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P168" s="2"/>
       <c r="Q168" t="s" s="2">
@@ -20969,7 +20966,7 @@
         <v>344</v>
       </c>
       <c r="AA168" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AB168" t="s" s="2">
         <v>20</v>
@@ -20987,7 +20984,7 @@
         <v>20</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>80</v>
@@ -21004,13 +21001,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -21033,16 +21030,16 @@
         <v>20</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M169" t="s" s="2">
         <v>258</v>
       </c>
       <c r="N169" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="O169" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P169" s="2"/>
       <c r="Q169" t="s" s="2">
@@ -21092,7 +21089,7 @@
         <v>20</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>73</v>
@@ -21109,13 +21106,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -21141,13 +21138,13 @@
         <v>337</v>
       </c>
       <c r="M170" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N170" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="N170" t="s" s="2">
+      <c r="O170" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="P170" s="2"/>
       <c r="Q170" t="s" s="2">
@@ -21197,7 +21194,7 @@
         <v>20</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>73</v>
@@ -21214,13 +21211,13 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -21243,13 +21240,13 @@
         <v>20</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M171" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N171" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
@@ -21300,7 +21297,7 @@
         <v>20</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>73</v>
@@ -21317,13 +21314,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -21349,13 +21346,13 @@
         <v>229</v>
       </c>
       <c r="M172" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N172" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N172" t="s" s="2">
+      <c r="O172" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="P172" s="2"/>
       <c r="Q172" t="s" s="2">
@@ -21405,7 +21402,7 @@
         <v>20</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>73</v>
@@ -21422,13 +21419,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -21454,10 +21451,10 @@
         <v>75</v>
       </c>
       <c r="M173" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N173" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
@@ -21508,7 +21505,7 @@
         <v>20</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AH173" t="s" s="2">
         <v>73</v>
@@ -21520,18 +21517,18 @@
         <v>20</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -21630,13 +21627,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -21733,13 +21730,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -21838,13 +21835,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -21943,13 +21940,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -22048,13 +22045,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -22153,13 +22150,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -22258,13 +22255,13 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -22365,13 +22362,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
@@ -22397,10 +22394,10 @@
         <v>138</v>
       </c>
       <c r="M182" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N182" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
@@ -22451,7 +22448,7 @@
         <v>20</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>73</v>
@@ -22468,13 +22465,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
@@ -22500,20 +22497,20 @@
         <v>337</v>
       </c>
       <c r="M183" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="N183" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="N183" t="s" s="2">
+      <c r="O183" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="P183" s="2"/>
       <c r="Q183" t="s" s="2">
         <v>20</v>
       </c>
       <c r="R183" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="S183" t="s" s="2">
         <v>20</v>
@@ -22558,7 +22555,7 @@
         <v>20</v>
       </c>
       <c r="AG183" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AH183" t="s" s="2">
         <v>73</v>
@@ -22575,13 +22572,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -22604,16 +22601,16 @@
         <v>81</v>
       </c>
       <c r="L184" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M184" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="M184" t="s" s="2">
+      <c r="N184" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="N184" t="s" s="2">
+      <c r="O184" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="P184" s="2"/>
       <c r="Q184" t="s" s="2">
@@ -22663,7 +22660,7 @@
         <v>20</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AH184" t="s" s="2">
         <v>73</v>
@@ -22680,13 +22677,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
@@ -22709,16 +22706,16 @@
         <v>20</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="M185" t="s" s="2">
+      <c r="N185" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="N185" t="s" s="2">
+      <c r="O185" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="O185" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="P185" s="2"/>
       <c r="Q185" t="s" s="2">
@@ -22768,7 +22765,7 @@
         <v>20</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>73</v>
@@ -22785,17 +22782,17 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F186" s="2"/>
       <c r="G186" t="s" s="2">
@@ -22817,13 +22814,13 @@
         <v>149</v>
       </c>
       <c r="M186" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="N186" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="N186" t="s" s="2">
+      <c r="O186" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="O186" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="P186" s="2"/>
       <c r="Q186" t="s" s="2">
@@ -22852,7 +22849,7 @@
         <v>152</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>164</v>
@@ -22873,7 +22870,7 @@
         <v>20</v>
       </c>
       <c r="AG186" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AH186" t="s" s="2">
         <v>73</v>
@@ -22890,17 +22887,17 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F187" s="2"/>
       <c r="G187" t="s" s="2">
@@ -22922,10 +22919,10 @@
         <v>149</v>
       </c>
       <c r="M187" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N187" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" s="2"/>
@@ -22974,7 +22971,7 @@
         <v>20</v>
       </c>
       <c r="AG187" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AH187" t="s" s="2">
         <v>73</v>
@@ -22991,13 +22988,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -23023,10 +23020,10 @@
         <v>149</v>
       </c>
       <c r="M188" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N188" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" s="2"/>
@@ -23056,7 +23053,7 @@
         <v>158</v>
       </c>
       <c r="Z188" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>176</v>
@@ -23077,7 +23074,7 @@
         <v>20</v>
       </c>
       <c r="AG188" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AH188" t="s" s="2">
         <v>73</v>
@@ -23094,13 +23091,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -23123,13 +23120,13 @@
         <v>81</v>
       </c>
       <c r="L189" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M189" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M189" t="s" s="2">
+      <c r="N189" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" s="2"/>
@@ -23180,7 +23177,7 @@
         <v>20</v>
       </c>
       <c r="AG189" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AH189" t="s" s="2">
         <v>73</v>
@@ -23197,13 +23194,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -23229,10 +23226,10 @@
         <v>194</v>
       </c>
       <c r="M190" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N190" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" s="2"/>
@@ -23283,7 +23280,7 @@
         <v>20</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AH190" t="s" s="2">
         <v>73</v>
@@ -23300,13 +23297,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -23329,16 +23326,16 @@
         <v>81</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M191" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N191" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="N191" t="s" s="2">
+      <c r="O191" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="P191" s="2"/>
       <c r="Q191" t="s" s="2">
@@ -23388,7 +23385,7 @@
         <v>20</v>
       </c>
       <c r="AG191" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AH191" t="s" s="2">
         <v>73</v>
@@ -23405,13 +23402,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -23434,13 +23431,13 @@
         <v>20</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M192" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N192" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
@@ -23491,7 +23488,7 @@
         <v>20</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AH192" t="s" s="2">
         <v>73</v>
@@ -23508,13 +23505,13 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -23537,13 +23534,13 @@
         <v>81</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="M193" t="s" s="2">
+      <c r="N193" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" s="2"/>
@@ -23594,7 +23591,7 @@
         <v>20</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>73</v>
@@ -23611,13 +23608,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -23640,19 +23637,19 @@
         <v>20</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M194" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M194" t="s" s="2">
+      <c r="N194" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="N194" t="s" s="2">
+      <c r="O194" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="O194" t="s" s="2">
+      <c r="P194" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="P194" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="Q194" t="s" s="2">
         <v>20</v>
@@ -23701,7 +23698,7 @@
         <v>20</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>73</v>
@@ -23718,13 +23715,13 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -23747,16 +23744,16 @@
         <v>20</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="M195" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="N195" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="N195" t="s" s="2">
+      <c r="O195" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="P195" s="2"/>
       <c r="Q195" t="s" s="2">
@@ -23806,7 +23803,7 @@
         <v>20</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>73</v>
@@ -23823,13 +23820,13 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -23855,13 +23852,13 @@
         <v>149</v>
       </c>
       <c r="M196" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="N196" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="N196" t="s" s="2">
+      <c r="O196" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="P196" s="2"/>
       <c r="Q196" t="s" s="2">
@@ -23890,10 +23887,10 @@
         <v>152</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AA196" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AB196" t="s" s="2">
         <v>20</v>
@@ -23911,7 +23908,7 @@
         <v>20</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AH196" t="s" s="2">
         <v>73</v>
@@ -23928,13 +23925,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -23960,10 +23957,10 @@
         <v>275</v>
       </c>
       <c r="M197" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N197" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
@@ -24014,7 +24011,7 @@
         <v>20</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AH197" t="s" s="2">
         <v>73</v>
@@ -24031,13 +24028,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -24134,13 +24131,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -24239,13 +24236,13 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -24346,13 +24343,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -24378,10 +24375,10 @@
         <v>149</v>
       </c>
       <c r="M201" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N201" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" s="2"/>
@@ -24411,7 +24408,7 @@
         <v>152</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>20</v>
@@ -24432,7 +24429,7 @@
         <v>20</v>
       </c>
       <c r="AG201" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AH201" t="s" s="2">
         <v>73</v>
@@ -24449,13 +24446,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -24478,16 +24475,16 @@
         <v>20</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M202" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N202" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="N202" t="s" s="2">
+      <c r="O202" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="O202" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="P202" s="2"/>
       <c r="Q202" t="s" s="2">
@@ -24537,7 +24534,7 @@
         <v>20</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AH202" t="s" s="2">
         <v>73</v>
@@ -24554,13 +24551,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -24586,13 +24583,13 @@
         <v>149</v>
       </c>
       <c r="M203" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="N203" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="N203" t="s" s="2">
+      <c r="O203" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="O203" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="P203" s="2"/>
       <c r="Q203" t="s" s="2">
@@ -24621,11 +24618,11 @@
         <v>152</v>
       </c>
       <c r="Z203" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AA203" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="AA203" t="s" s="2">
-        <v>678</v>
-      </c>
       <c r="AB203" t="s" s="2">
         <v>20</v>
       </c>
@@ -24642,7 +24639,7 @@
         <v>20</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>73</v>
@@ -24659,13 +24656,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -24691,13 +24688,13 @@
         <v>149</v>
       </c>
       <c r="M204" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="N204" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="N204" t="s" s="2">
+      <c r="O204" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="P204" s="2"/>
       <c r="Q204" t="s" s="2">
@@ -24726,11 +24723,11 @@
         <v>152</v>
       </c>
       <c r="Z204" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AA204" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="AA204" t="s" s="2">
-        <v>684</v>
-      </c>
       <c r="AB204" t="s" s="2">
         <v>20</v>
       </c>
@@ -24747,7 +24744,7 @@
         <v>20</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>73</v>
@@ -24764,13 +24761,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -24796,13 +24793,13 @@
         <v>149</v>
       </c>
       <c r="M205" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N205" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="N205" t="s" s="2">
+      <c r="O205" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="O205" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="P205" s="2"/>
       <c r="Q205" t="s" s="2">
@@ -24852,7 +24849,7 @@
         <v>20</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>73</v>
@@ -24869,13 +24866,13 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -24901,10 +24898,10 @@
         <v>149</v>
       </c>
       <c r="M206" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="N206" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" s="2"/>
@@ -24934,11 +24931,11 @@
         <v>152</v>
       </c>
       <c r="Z206" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AA206" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="AA206" t="s" s="2">
-        <v>693</v>
-      </c>
       <c r="AB206" t="s" s="2">
         <v>20</v>
       </c>
@@ -24955,7 +24952,7 @@
         <v>20</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>73</v>
@@ -24972,13 +24969,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -25004,10 +25001,10 @@
         <v>337</v>
       </c>
       <c r="M207" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="N207" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" s="2"/>
@@ -25058,7 +25055,7 @@
         <v>20</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>73</v>
@@ -25075,13 +25072,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -25104,16 +25101,16 @@
         <v>20</v>
       </c>
       <c r="L208" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M208" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="M208" t="s" s="2">
+      <c r="N208" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="N208" t="s" s="2">
+      <c r="O208" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="O208" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="P208" s="2"/>
       <c r="Q208" t="s" s="2">
@@ -25163,7 +25160,7 @@
         <v>20</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>73</v>
@@ -25180,13 +25177,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -25209,13 +25206,13 @@
         <v>20</v>
       </c>
       <c r="L209" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M209" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="M209" t="s" s="2">
+      <c r="N209" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="N209" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="O209" s="2"/>
       <c r="P209" s="2"/>
@@ -25266,7 +25263,7 @@
         <v>20</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>73</v>
@@ -25283,17 +25280,17 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F210" s="2"/>
       <c r="G210" t="s" s="2">
@@ -25315,10 +25312,10 @@
         <v>75</v>
       </c>
       <c r="M210" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="N210" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="N210" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" s="2"/>
@@ -25369,7 +25366,7 @@
         <v>20</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>73</v>
@@ -25381,18 +25378,18 @@
         <v>20</v>
       </c>
       <c r="AK210" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -25491,13 +25488,13 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -25594,13 +25591,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -25699,13 +25696,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -25804,13 +25801,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -25909,13 +25906,13 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
@@ -26014,13 +26011,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -26119,13 +26116,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -26226,13 +26223,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -26261,7 +26258,7 @@
         <v>139</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" s="2"/>
@@ -26312,7 +26309,7 @@
         <v>20</v>
       </c>
       <c r="AG219" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AH219" t="s" s="2">
         <v>73</v>
@@ -26329,13 +26326,13 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -26361,20 +26358,20 @@
         <v>337</v>
       </c>
       <c r="M220" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="N220" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="N220" t="s" s="2">
-        <v>727</v>
-      </c>
       <c r="O220" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="P220" s="2"/>
       <c r="Q220" t="s" s="2">
         <v>20</v>
       </c>
       <c r="R220" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="S220" t="s" s="2">
         <v>20</v>
@@ -26419,7 +26416,7 @@
         <v>20</v>
       </c>
       <c r="AG220" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AH220" t="s" s="2">
         <v>73</v>
@@ -26436,13 +26433,13 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" t="s" s="2">
@@ -26468,7 +26465,7 @@
         <v>149</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="N221" t="s" s="2">
         <v>163</v>
@@ -26520,7 +26517,7 @@
         <v>20</v>
       </c>
       <c r="AG221" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AH221" t="s" s="2">
         <v>73</v>
@@ -26537,13 +26534,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" t="s" s="2">
@@ -26566,10 +26563,10 @@
         <v>81</v>
       </c>
       <c r="L222" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="M222" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="M222" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="N222" t="s" s="2">
         <v>168</v>
@@ -26621,7 +26618,7 @@
         <v>20</v>
       </c>
       <c r="AG222" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AH222" t="s" s="2">
         <v>73</v>
@@ -26638,13 +26635,13 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" t="s" s="2">
@@ -26670,7 +26667,7 @@
         <v>149</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="N223" t="s" s="2">
         <v>174</v>
@@ -26703,7 +26700,7 @@
         <v>158</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>176</v>
@@ -26724,7 +26721,7 @@
         <v>20</v>
       </c>
       <c r="AG223" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>73</v>
@@ -26741,13 +26738,13 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" t="s" s="2">
@@ -26773,13 +26770,13 @@
         <v>194</v>
       </c>
       <c r="M224" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="N224" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="N224" t="s" s="2">
+      <c r="O224" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="O224" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="P224" s="2"/>
       <c r="Q224" t="s" s="2">
@@ -26829,7 +26826,7 @@
         <v>20</v>
       </c>
       <c r="AG224" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AH224" t="s" s="2">
         <v>73</v>
@@ -26846,13 +26843,13 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -26875,16 +26872,16 @@
         <v>81</v>
       </c>
       <c r="L225" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="M225" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="M225" t="s" s="2">
+      <c r="N225" t="s" s="2">
         <v>742</v>
       </c>
-      <c r="N225" t="s" s="2">
+      <c r="O225" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="O225" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="P225" s="2"/>
       <c r="Q225" t="s" s="2">
@@ -26934,7 +26931,7 @@
         <v>20</v>
       </c>
       <c r="AG225" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AH225" t="s" s="2">
         <v>80</v>
@@ -26951,13 +26948,13 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -26983,10 +26980,10 @@
         <v>233</v>
       </c>
       <c r="M226" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="N226" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="N226" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="O226" s="2"/>
       <c r="P226" s="2"/>
@@ -27037,7 +27034,7 @@
         <v>20</v>
       </c>
       <c r="AG226" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AH226" t="s" s="2">
         <v>73</v>
@@ -27054,13 +27051,13 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" t="s" s="2">
@@ -27083,13 +27080,13 @@
         <v>20</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M227" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="N227" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="O227" s="2"/>
       <c r="P227" s="2"/>
@@ -27140,7 +27137,7 @@
         <v>20</v>
       </c>
       <c r="AG227" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AH227" t="s" s="2">
         <v>73</v>
@@ -27157,13 +27154,13 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
@@ -27189,10 +27186,10 @@
         <v>75</v>
       </c>
       <c r="M228" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="N228" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="N228" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="O228" s="2"/>
       <c r="P228" s="2"/>
@@ -27243,7 +27240,7 @@
         <v>20</v>
       </c>
       <c r="AG228" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AH228" t="s" s="2">
         <v>73</v>
@@ -27255,18 +27252,18 @@
         <v>20</v>
       </c>
       <c r="AK228" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -27365,13 +27362,13 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -27468,13 +27465,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -27573,13 +27570,13 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -27678,13 +27675,13 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -27783,13 +27780,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
@@ -27888,13 +27885,13 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -27993,13 +27990,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -28100,13 +28097,13 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -28135,7 +28132,7 @@
         <v>139</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="O237" s="2"/>
       <c r="P237" s="2"/>
@@ -28186,7 +28183,7 @@
         <v>20</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AH237" t="s" s="2">
         <v>73</v>
@@ -28203,13 +28200,13 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" t="s" s="2">
@@ -28287,7 +28284,7 @@
         <v>20</v>
       </c>
       <c r="AG238" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="AH238" t="s" s="2">
         <v>73</v>
@@ -28304,13 +28301,13 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" t="s" s="2">
@@ -28336,10 +28333,10 @@
         <v>166</v>
       </c>
       <c r="M239" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="N239" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="N239" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="O239" s="2"/>
       <c r="P239" s="2"/>
@@ -28388,7 +28385,7 @@
         <v>20</v>
       </c>
       <c r="AG239" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AH239" t="s" s="2">
         <v>73</v>
@@ -28405,13 +28402,13 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" t="s" s="2">
@@ -28470,7 +28467,7 @@
         <v>158</v>
       </c>
       <c r="Z240" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AA240" t="s" s="2">
         <v>176</v>
@@ -28491,7 +28488,7 @@
         <v>20</v>
       </c>
       <c r="AG240" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AH240" t="s" s="2">
         <v>73</v>
@@ -28508,13 +28505,13 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" t="s" s="2">
@@ -28540,13 +28537,13 @@
         <v>149</v>
       </c>
       <c r="M241" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="N241" t="s" s="2">
         <v>775</v>
       </c>
-      <c r="N241" t="s" s="2">
+      <c r="O241" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="O241" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="P241" s="2"/>
       <c r="Q241" t="s" s="2">
@@ -28594,7 +28591,7 @@
         <v>20</v>
       </c>
       <c r="AG241" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AH241" t="s" s="2">
         <v>73</v>
@@ -28611,13 +28608,13 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" t="s" s="2">
@@ -28640,13 +28637,13 @@
         <v>81</v>
       </c>
       <c r="L242" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="M242" t="s" s="2">
         <v>779</v>
       </c>
-      <c r="M242" t="s" s="2">
+      <c r="N242" t="s" s="2">
         <v>780</v>
-      </c>
-      <c r="N242" t="s" s="2">
-        <v>781</v>
       </c>
       <c r="O242" s="2"/>
       <c r="P242" s="2"/>
@@ -28697,7 +28694,7 @@
         <v>20</v>
       </c>
       <c r="AG242" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="AH242" t="s" s="2">
         <v>80</v>
@@ -28714,13 +28711,13 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" t="s" s="2">
@@ -28746,10 +28743,10 @@
         <v>100</v>
       </c>
       <c r="M243" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="N243" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="N243" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="O243" s="2"/>
       <c r="P243" s="2"/>
@@ -28779,11 +28776,11 @@
         <v>104</v>
       </c>
       <c r="Z243" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AA243" t="s" s="2">
         <v>785</v>
       </c>
-      <c r="AA243" t="s" s="2">
-        <v>786</v>
-      </c>
       <c r="AB243" t="s" s="2">
         <v>20</v>
       </c>
@@ -28800,7 +28797,7 @@
         <v>20</v>
       </c>
       <c r="AG243" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AH243" t="s" s="2">
         <v>80</v>
@@ -28817,13 +28814,13 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D244" s="2"/>
       <c r="E244" t="s" s="2">
@@ -28849,10 +28846,10 @@
         <v>220</v>
       </c>
       <c r="M244" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="N244" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="N244" t="s" s="2">
-        <v>789</v>
       </c>
       <c r="O244" s="2"/>
       <c r="P244" s="2"/>
@@ -28903,7 +28900,7 @@
         <v>20</v>
       </c>
       <c r="AG244" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AH244" t="s" s="2">
         <v>80</v>
@@ -28920,13 +28917,13 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D245" s="2"/>
       <c r="E245" t="s" s="2">
@@ -28952,10 +28949,10 @@
         <v>220</v>
       </c>
       <c r="M245" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="N245" t="s" s="2">
         <v>791</v>
-      </c>
-      <c r="N245" t="s" s="2">
-        <v>792</v>
       </c>
       <c r="O245" s="2"/>
       <c r="P245" s="2"/>
@@ -29006,7 +29003,7 @@
         <v>20</v>
       </c>
       <c r="AG245" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AH245" t="s" s="2">
         <v>80</v>
@@ -29023,13 +29020,13 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D246" s="2"/>
       <c r="E246" t="s" s="2">
@@ -29055,10 +29052,10 @@
         <v>337</v>
       </c>
       <c r="M246" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="N246" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="N246" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="O246" s="2"/>
       <c r="P246" s="2"/>
@@ -29066,7 +29063,7 @@
         <v>20</v>
       </c>
       <c r="R246" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="S246" t="s" s="2">
         <v>20</v>
@@ -29111,7 +29108,7 @@
         <v>20</v>
       </c>
       <c r="AG246" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AH246" t="s" s="2">
         <v>73</v>
@@ -29128,13 +29125,13 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D247" s="2"/>
       <c r="E247" t="s" s="2">
@@ -29160,10 +29157,10 @@
         <v>194</v>
       </c>
       <c r="M247" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="N247" t="s" s="2">
         <v>798</v>
-      </c>
-      <c r="N247" t="s" s="2">
-        <v>799</v>
       </c>
       <c r="O247" s="2"/>
       <c r="P247" s="2"/>
@@ -29214,7 +29211,7 @@
         <v>20</v>
       </c>
       <c r="AG247" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AH247" t="s" s="2">
         <v>73</v>

--- a/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-08T14:41:39+00:00</t>
+    <t>2025-03-08T14:51:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
